--- a/Personal_expense_Analysis.xlsx
+++ b/Personal_expense_Analysis.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rathnaa K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F6D24C-6A92-4E5D-944B-A8CECC2CD980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA99355-D5C6-4A9A-B6BA-219BD1EF1CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Analysis" sheetId="5" r:id="rId2"/>
+    <sheet name="Analysis" sheetId="6" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Day">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId4"/>
+        <x14:slicerCache r:id="rId5"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -169,13 +170,19 @@
   <si>
     <t>Personal Expense Analysis Dashboard</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of Amount (INR)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -214,7 +221,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -222,11 +229,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -237,25 +259,2753 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
+  <dxfs count="229">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="21" formatCode="dd/mmm"/>
@@ -265,149 +3015,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="&quot;₹&quot;\ #,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="&quot;₹&quot;\ #,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;\ * #,##0.0_ ;_ &quot;₹&quot;\ * \-#,##0.0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;\ * #,##0.0_ ;_ &quot;₹&quot;\ * \-#,##0.0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -436,7 +3044,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Personal_expense_Analysis.xlsx]Analysis!PivotTable5</c:name>
+    <c:name>[Personal_expense_Analysis.xlsx]Dashboard!PivotTable5</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -634,8 +3242,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1158,7 +3765,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Analysis!$B$6</c:f>
+              <c:f>Dashboard!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1508,7 +4115,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$A$7:$A$13</c:f>
+              <c:f>Dashboard!$A$6:$A$12</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1534,7 +4141,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$B$7:$B$13</c:f>
+              <c:f>Dashboard!$B$6:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1629,7 +4236,9 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1656,7 +4265,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -1675,12 +4283,16 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="107"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="7"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Personal_expense_Analysis.xlsx]Analysis!PivotTable1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1689,12 +4301,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1702,13 +4311,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Daily</a:t>
+              <a:rPr lang="en-US" sz="1600" b="1" baseline="0"/>
+              <a:t>SPENDING TREND BY DATE</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-IN" baseline="0"/>
-              <a:t> spending trend</a:t>
-            </a:r>
+            <a:endParaRPr lang="en-US" sz="1600" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1725,12 +4331,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+            <a:defRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1742,60 +4345,261 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="stacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Raw_Data!$D$1</c:f>
+              <c:f>Analysis!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Amount (INR)</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent5"/>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>Raw_Data!$A:$A</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>Raw_Data!$A$2:$A$1048576</c:f>
+              <c:f>Analysis!$A$2:$A$32</c:f>
               <c:strCache>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
@@ -1893,102 +4697,98 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>Raw_Data!$D$2:$D$31</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>Raw_Data!$D$3:$D$31</c:f>
+              <c:f>Analysis!$B$2:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>1500</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>450</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>499</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>800</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>220</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>1000</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>280</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>299</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>70</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>350</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>210</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>320</c:v>
                 </c:pt>
               </c:numCache>
@@ -1997,12 +4797,11 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DAB5-4E5E-B660-2EED417A3F83}"/>
+              <c16:uniqueId val="{00000000-A807-4962-A648-05B6B595B957}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2012,18 +4811,18 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="370325519"/>
-        <c:axId val="370326479"/>
+        <c:axId val="844359280"/>
+        <c:axId val="784678128"/>
       </c:lineChart>
-      <c:dateAx>
-        <c:axId val="370325519"/>
+      <c:catAx>
+        <c:axId val="844359280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="d\-mmm" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="dd/mm" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -2044,12 +4843,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2059,47 +4855,28 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="370326479"/>
+        <c:crossAx val="784678128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="370326479"/>
+        <c:axId val="784678128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -2108,12 +4885,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2123,7 +4897,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="370325519"/>
+        <c:crossAx val="844359280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2136,7 +4910,7 @@
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -2148,10 +4922,12 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -2161,7 +4937,14 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="tx2"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2171,6 +4954,20 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
 </c:chartSpace>
 </file>
 
@@ -2181,8 +4978,42 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="25">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -2655,7 +5486,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="239">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2666,7 +5497,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -2689,18 +5520,18 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="bg1"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
@@ -2712,7 +5543,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -2720,11 +5551,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -2756,45 +5587,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="22225" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2806,34 +5627,30 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2855,13 +5672,15 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2876,15 +5695,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2895,16 +5714,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2913,10 +5733,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
@@ -2932,15 +5752,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2959,16 +5785,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2977,16 +5804,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2995,16 +5823,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -3025,7 +5854,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -3033,7 +5862,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -3046,17 +5875,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -3064,10 +5882,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -3088,7 +5906,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3097,14 +5915,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDash"/>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3118,7 +5936,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="800" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
@@ -3134,8 +5952,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -3151,17 +5969,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -3169,8 +5976,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3180,15 +5993,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
+      <xdr:colOff>475307</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>148817</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>8466</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>446051</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
+      <xdr:rowOff>155168</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3215,54 +6028,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>3772</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>16933</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>482852</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>120713</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>736599</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0178176D-E994-42E9-906B-E26910FE5F9B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>445130</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>143346</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3277,8 +6052,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3009900" y="3819525"/>
-          <a:ext cx="5191125" cy="882650"/>
+          <a:off x="2685862" y="3742099"/>
+          <a:ext cx="5137842" cy="927980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3412,18 +6187,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>356982</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>126965</xdr:rowOff>
+      <xdr:colOff>371923</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>74968</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>864</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>167981</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1298453</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>179591</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Day">
@@ -3446,7 +6221,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3456,8 +6231,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="356982" y="2687285"/>
-              <a:ext cx="1823202" cy="2418456"/>
+              <a:off x="371923" y="2428869"/>
+              <a:ext cx="1824332" cy="2277455"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3487,17 +6262,116 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>80105</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>150891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>475307</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>135802</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A61AEFB1-5BEA-4BD4-91F3-3F048430D709}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Rathnaa K" refreshedDate="46127.778330555557" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{97525758-462C-49C3-B793-0AB4A4F35637}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Rathnaa K" refreshedDate="46292.988481944441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{97525758-462C-49C3-B793-0AB4A4F35637}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
   <cacheFields count="6">
-    <cacheField name="Date" numFmtId="0">
-      <sharedItems/>
+    <cacheField name="Date" numFmtId="16">
+      <sharedItems containsNonDate="0" containsDate="1" containsMixedTypes="1" minDate="2026-03-01T00:00:00" maxDate="2026-03-31T00:00:00" count="60">
+        <d v="2026-03-01T00:00:00"/>
+        <d v="2026-03-02T00:00:00"/>
+        <d v="2026-03-03T00:00:00"/>
+        <d v="2026-03-04T00:00:00"/>
+        <d v="2026-03-05T00:00:00"/>
+        <d v="2026-03-06T00:00:00"/>
+        <d v="2026-03-07T00:00:00"/>
+        <d v="2026-03-08T00:00:00"/>
+        <d v="2026-03-09T00:00:00"/>
+        <d v="2026-03-10T00:00:00"/>
+        <d v="2026-03-11T00:00:00"/>
+        <d v="2026-03-12T00:00:00"/>
+        <d v="2026-03-13T00:00:00"/>
+        <d v="2026-03-14T00:00:00"/>
+        <d v="2026-03-15T00:00:00"/>
+        <d v="2026-03-16T00:00:00"/>
+        <d v="2026-03-17T00:00:00"/>
+        <d v="2026-03-18T00:00:00"/>
+        <d v="2026-03-19T00:00:00"/>
+        <d v="2026-03-20T00:00:00"/>
+        <d v="2026-03-21T00:00:00"/>
+        <d v="2026-03-22T00:00:00"/>
+        <d v="2026-03-23T00:00:00"/>
+        <d v="2026-03-24T00:00:00"/>
+        <d v="2026-03-25T00:00:00"/>
+        <d v="2026-03-26T00:00:00"/>
+        <d v="2026-03-27T00:00:00"/>
+        <d v="2026-03-28T00:00:00"/>
+        <d v="2026-03-29T00:00:00"/>
+        <d v="2026-03-30T00:00:00"/>
+        <s v="2026-03-01" u="1"/>
+        <s v="2026-03-02" u="1"/>
+        <s v="2026-03-03" u="1"/>
+        <s v="2026-03-04" u="1"/>
+        <s v="2026-03-05" u="1"/>
+        <s v="2026-03-06" u="1"/>
+        <s v="2026-03-07" u="1"/>
+        <s v="2026-03-08" u="1"/>
+        <s v="2026-03-09" u="1"/>
+        <s v="2026-03-10" u="1"/>
+        <s v="2026-03-11" u="1"/>
+        <s v="2026-03-12" u="1"/>
+        <s v="2026-03-13" u="1"/>
+        <s v="2026-03-14" u="1"/>
+        <s v="2026-03-15" u="1"/>
+        <s v="2026-03-16" u="1"/>
+        <s v="2026-03-17" u="1"/>
+        <s v="2026-03-18" u="1"/>
+        <s v="2026-03-19" u="1"/>
+        <s v="2026-03-20" u="1"/>
+        <s v="2026-03-21" u="1"/>
+        <s v="2026-03-22" u="1"/>
+        <s v="2026-03-23" u="1"/>
+        <s v="2026-03-24" u="1"/>
+        <s v="2026-03-25" u="1"/>
+        <s v="2026-03-26" u="1"/>
+        <s v="2026-03-27" u="1"/>
+        <s v="2026-03-28" u="1"/>
+        <s v="2026-03-29" u="1"/>
+        <s v="2026-03-30" u="1"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
       <sharedItems count="6">
@@ -3510,67 +6384,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Description" numFmtId="0">
-      <sharedItems count="22">
-        <s v="Breakfast"/>
-        <s v="Bus fare"/>
-        <s v="Lunch"/>
-        <s v="Clothes"/>
-        <s v="Electricity"/>
-        <s v="Dinner"/>
-        <s v="Movie"/>
-        <s v="Snacks"/>
-        <s v="Auto"/>
-        <s v="Medicines"/>
-        <s v="Groceries"/>
-        <s v="Internet"/>
-        <s v="Metro"/>
-        <s v="Subscription"/>
-        <s v="Doctor Visit"/>
-        <s v="Accessories"/>
-        <s v="Fuel"/>
-        <s v="Mobile Recharge"/>
-        <s v="Games"/>
-        <s v="Cab"/>
-        <s v="Books"/>
-        <s v="Gym"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Amount (INR)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="1500" count="26">
-        <n v="120"/>
-        <n v="50"/>
-        <n v="180"/>
-        <n v="1200"/>
-        <n v="1500"/>
-        <n v="250"/>
-        <n v="300"/>
-        <n v="90"/>
-        <n v="450"/>
-        <n v="200"/>
-        <n v="850"/>
-        <n v="700"/>
-        <n v="100"/>
-        <n v="499"/>
-        <n v="110"/>
-        <n v="800"/>
-        <n v="220"/>
-        <n v="600"/>
-        <n v="1000"/>
-        <n v="280"/>
-        <n v="299"/>
-        <n v="70"/>
-        <n v="350"/>
-        <n v="210"/>
-        <n v="500"/>
-        <n v="320"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="1500"/>
     </cacheField>
     <cacheField name="Payment Mode" numFmtId="0">
-      <sharedItems count="3">
-        <s v="UPI"/>
-        <s v="Cash"/>
-        <s v="Card"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Day" numFmtId="0">
       <sharedItems count="7">
@@ -3595,251 +6415,472 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
   <r>
-    <s v="2026-03-01"/>
     <x v="0"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="Breakfast"/>
+    <n v="120"/>
+    <s v="UPI"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="2026-03-02"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
+    <s v="Bus fare"/>
+    <n v="50"/>
+    <s v="Cash"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="2026-03-03"/>
-    <x v="0"/>
-    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
+    <s v="Lunch"/>
+    <n v="180"/>
+    <s v="UPI"/>
     <x v="2"/>
   </r>
   <r>
-    <s v="2026-03-04"/>
-    <x v="2"/>
-    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
+    <s v="Clothes"/>
+    <n v="1200"/>
+    <s v="Card"/>
     <x v="3"/>
   </r>
   <r>
-    <s v="2026-03-05"/>
+    <x v="4"/>
     <x v="3"/>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="Electricity"/>
+    <n v="1500"/>
+    <s v="UPI"/>
     <x v="4"/>
   </r>
   <r>
-    <s v="2026-03-06"/>
-    <x v="0"/>
-    <x v="5"/>
     <x v="5"/>
     <x v="0"/>
+    <s v="Dinner"/>
+    <n v="250"/>
+    <s v="UPI"/>
     <x v="5"/>
   </r>
   <r>
-    <s v="2026-03-07"/>
+    <x v="6"/>
     <x v="4"/>
-    <x v="6"/>
-    <x v="6"/>
-    <x v="2"/>
+    <s v="Movie"/>
+    <n v="300"/>
+    <s v="Card"/>
     <x v="6"/>
   </r>
   <r>
-    <s v="2026-03-08"/>
+    <x v="7"/>
     <x v="0"/>
-    <x v="7"/>
-    <x v="7"/>
-    <x v="1"/>
+    <s v="Snacks"/>
+    <n v="90"/>
+    <s v="Cash"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="2026-03-09"/>
+    <x v="8"/>
     <x v="1"/>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="1"/>
+    <s v="Auto"/>
+    <n v="120"/>
+    <s v="Cash"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="2026-03-10"/>
+    <x v="9"/>
     <x v="5"/>
-    <x v="9"/>
-    <x v="8"/>
-    <x v="0"/>
+    <s v="Medicines"/>
+    <n v="450"/>
+    <s v="UPI"/>
     <x v="2"/>
   </r>
   <r>
-    <s v="2026-03-11"/>
+    <x v="10"/>
     <x v="0"/>
-    <x v="2"/>
-    <x v="9"/>
-    <x v="0"/>
+    <s v="Lunch"/>
+    <n v="200"/>
+    <s v="UPI"/>
     <x v="3"/>
   </r>
   <r>
-    <s v="2026-03-12"/>
+    <x v="11"/>
     <x v="2"/>
-    <x v="10"/>
-    <x v="10"/>
-    <x v="0"/>
+    <s v="Groceries"/>
+    <n v="850"/>
+    <s v="UPI"/>
     <x v="4"/>
   </r>
   <r>
-    <s v="2026-03-13"/>
+    <x v="12"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="11"/>
-    <x v="2"/>
+    <s v="Internet"/>
+    <n v="700"/>
+    <s v="Card"/>
     <x v="5"/>
   </r>
   <r>
-    <s v="2026-03-14"/>
+    <x v="13"/>
     <x v="0"/>
-    <x v="5"/>
-    <x v="6"/>
-    <x v="0"/>
+    <s v="Dinner"/>
+    <n v="300"/>
+    <s v="UPI"/>
     <x v="6"/>
   </r>
   <r>
-    <s v="2026-03-15"/>
+    <x v="14"/>
     <x v="1"/>
-    <x v="12"/>
-    <x v="12"/>
-    <x v="2"/>
+    <s v="Metro"/>
+    <n v="100"/>
+    <s v="Card"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="2026-03-16"/>
+    <x v="15"/>
     <x v="4"/>
-    <x v="13"/>
-    <x v="13"/>
-    <x v="2"/>
+    <s v="Subscription"/>
+    <n v="499"/>
+    <s v="Card"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="2026-03-17"/>
+    <x v="16"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="14"/>
-    <x v="1"/>
+    <s v="Breakfast"/>
+    <n v="110"/>
+    <s v="Cash"/>
     <x v="2"/>
   </r>
   <r>
-    <s v="2026-03-18"/>
+    <x v="17"/>
     <x v="5"/>
-    <x v="14"/>
-    <x v="15"/>
-    <x v="0"/>
+    <s v="Doctor Visit"/>
+    <n v="800"/>
+    <s v="UPI"/>
     <x v="3"/>
   </r>
   <r>
-    <s v="2026-03-19"/>
+    <x v="18"/>
     <x v="0"/>
-    <x v="2"/>
-    <x v="16"/>
-    <x v="0"/>
+    <s v="Lunch"/>
+    <n v="220"/>
+    <s v="UPI"/>
     <x v="4"/>
   </r>
   <r>
-    <s v="2026-03-20"/>
+    <x v="19"/>
     <x v="2"/>
-    <x v="15"/>
-    <x v="17"/>
-    <x v="2"/>
+    <s v="Accessories"/>
+    <n v="600"/>
+    <s v="Card"/>
     <x v="5"/>
   </r>
   <r>
-    <s v="2026-03-21"/>
+    <x v="20"/>
     <x v="1"/>
-    <x v="16"/>
-    <x v="18"/>
-    <x v="0"/>
+    <s v="Fuel"/>
+    <n v="1000"/>
+    <s v="UPI"/>
     <x v="6"/>
   </r>
   <r>
-    <s v="2026-03-22"/>
+    <x v="21"/>
     <x v="0"/>
-    <x v="5"/>
-    <x v="19"/>
-    <x v="0"/>
+    <s v="Dinner"/>
+    <n v="280"/>
+    <s v="UPI"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="2026-03-23"/>
+    <x v="22"/>
     <x v="3"/>
-    <x v="17"/>
-    <x v="20"/>
-    <x v="0"/>
+    <s v="Mobile Recharge"/>
+    <n v="299"/>
+    <s v="UPI"/>
     <x v="1"/>
   </r>
   <r>
-    <s v="2026-03-24"/>
+    <x v="23"/>
     <x v="0"/>
-    <x v="7"/>
-    <x v="21"/>
-    <x v="1"/>
+    <s v="Snacks"/>
+    <n v="70"/>
+    <s v="Cash"/>
     <x v="2"/>
   </r>
   <r>
-    <s v="2026-03-25"/>
+    <x v="24"/>
     <x v="4"/>
-    <x v="18"/>
-    <x v="9"/>
-    <x v="0"/>
+    <s v="Games"/>
+    <n v="200"/>
+    <s v="UPI"/>
     <x v="3"/>
   </r>
   <r>
-    <s v="2026-03-26"/>
+    <x v="25"/>
     <x v="1"/>
-    <x v="19"/>
-    <x v="22"/>
-    <x v="2"/>
+    <s v="Cab"/>
+    <n v="350"/>
+    <s v="Card"/>
     <x v="4"/>
   </r>
   <r>
-    <s v="2026-03-27"/>
+    <x v="26"/>
     <x v="0"/>
-    <x v="2"/>
-    <x v="23"/>
-    <x v="0"/>
+    <s v="Lunch"/>
+    <n v="210"/>
+    <s v="UPI"/>
     <x v="5"/>
   </r>
   <r>
-    <s v="2026-03-28"/>
+    <x v="27"/>
     <x v="2"/>
-    <x v="20"/>
-    <x v="24"/>
-    <x v="2"/>
+    <s v="Books"/>
+    <n v="500"/>
+    <s v="Card"/>
     <x v="6"/>
   </r>
   <r>
-    <s v="2026-03-29"/>
+    <x v="28"/>
     <x v="5"/>
-    <x v="21"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="Gym"/>
+    <n v="1200"/>
+    <s v="UPI"/>
     <x v="0"/>
   </r>
   <r>
-    <s v="2026-03-30"/>
+    <x v="29"/>
     <x v="0"/>
-    <x v="5"/>
-    <x v="25"/>
-    <x v="0"/>
+    <s v="Dinner"/>
+    <n v="320"/>
+    <s v="UPI"/>
     <x v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{628AA830-04D5-436D-9F1A-33B3ED394B1E}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21" rowHeaderCaption="Category" fieldListSortAscending="1">
-  <location ref="A6:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38B4BE5F-4934-4A42-B391-5B1115592FE9}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A1:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" numFmtId="16" showAll="0" defaultSubtotal="0">
+      <items count="60">
+        <item m="1" x="30"/>
+        <item m="1" x="31"/>
+        <item m="1" x="32"/>
+        <item m="1" x="33"/>
+        <item m="1" x="34"/>
+        <item m="1" x="35"/>
+        <item m="1" x="36"/>
+        <item m="1" x="37"/>
+        <item m="1" x="38"/>
+        <item m="1" x="39"/>
+        <item m="1" x="40"/>
+        <item m="1" x="41"/>
+        <item m="1" x="42"/>
+        <item m="1" x="43"/>
+        <item m="1" x="44"/>
+        <item m="1" x="45"/>
+        <item m="1" x="46"/>
+        <item m="1" x="47"/>
+        <item m="1" x="48"/>
+        <item m="1" x="49"/>
+        <item m="1" x="50"/>
+        <item m="1" x="51"/>
+        <item m="1" x="52"/>
+        <item m="1" x="53"/>
+        <item m="1" x="54"/>
+        <item m="1" x="55"/>
+        <item m="1" x="56"/>
+        <item m="1" x="57"/>
+        <item m="1" x="58"/>
+        <item m="1" x="59"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="31">
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount (INR)" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{628AA830-04D5-436D-9F1A-33B3ED394B1E}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25" rowHeaderCaption="Category" fieldListSortAscending="1">
+  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -3862,72 +6903,9 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField showAll="0">
-      <items count="23">
-        <item x="15"/>
-        <item x="8"/>
-        <item x="20"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="4"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="10"/>
-        <item x="21"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="27">
-        <item x="1"/>
-        <item x="21"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="23"/>
-        <item x="16"/>
-        <item x="5"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item x="25"/>
-        <item x="22"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="24"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField multipleItemSelectionAllowed="1" showAll="0">
       <items count="8">
         <item x="0"/>
@@ -3971,11 +6949,55 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total Spending (INR)" fld="3" baseField="1" baseItem="0" numFmtId="172"/>
+    <dataField name="Total Spending (INR)" fld="3" baseField="1" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="22">
+  <formats count="13">
+    <format dxfId="220">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="219">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="218">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="217">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="216">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="215">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="214">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="213">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="212">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="211">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="210">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="209">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="208">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="7">
@@ -4077,6 +7099,7 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Day" xr10:uid="{26CB9897-0B20-428A-AAF5-68A59B650652}" sourceName="Day">
   <pivotTables>
     <pivotTable tabId="5" name="PivotTable5"/>
+    <pivotTable tabId="6" name="PivotTable1"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1353721506">
@@ -4101,15 +7124,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{235D1509-99A6-4033-973D-7C7CCBAD6BEB}" name="Table1" displayName="Table1" ref="A1:F31" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{235D1509-99A6-4033-973D-7C7CCBAD6BEB}" name="Table1" displayName="Table1" ref="A1:F31" totalsRowShown="0" headerRowDxfId="228" dataDxfId="227">
   <autoFilter ref="A1:F31" xr:uid="{235D1509-99A6-4033-973D-7C7CCBAD6BEB}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A7C6435C-D9A7-44D8-8C95-2CE92E5E2904}" name="Date" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{A6D28EEA-A76D-4D44-A0CB-953E8281E9A4}" name="Category" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{7CD5662E-DADD-4B39-9996-1DAEA80A3CDE}" name="Description" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{B09E391B-BB2E-482E-85B2-9841EA6CAF7E}" name="Amount (INR)" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{BD4664E9-1AF6-4522-BABD-F91FBFB3A0B2}" name="Payment Mode" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{CA9732C9-F34C-4D51-8F04-CC705B99CD3A}" name="Day" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{A7C6435C-D9A7-44D8-8C95-2CE92E5E2904}" name="Date" dataDxfId="226"/>
+    <tableColumn id="2" xr3:uid="{A6D28EEA-A76D-4D44-A0CB-953E8281E9A4}" name="Category" dataDxfId="225"/>
+    <tableColumn id="3" xr3:uid="{7CD5662E-DADD-4B39-9996-1DAEA80A3CDE}" name="Description" dataDxfId="224"/>
+    <tableColumn id="4" xr3:uid="{B09E391B-BB2E-482E-85B2-9841EA6CAF7E}" name="Amount (INR)" dataDxfId="223"/>
+    <tableColumn id="5" xr3:uid="{BD4664E9-1AF6-4522-BABD-F91FBFB3A0B2}" name="Payment Mode" dataDxfId="222"/>
+    <tableColumn id="6" xr3:uid="{CA9732C9-F34C-4D51-8F04-CC705B99CD3A}" name="Day" dataDxfId="221">
       <calculatedColumnFormula>TEXT(Table1[[#This Row],[Date]],"dddd")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4405,11 +7428,11 @@
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.88671875" bestFit="1" customWidth="1"/>
@@ -4418,27 +7441,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="4">
         <v>46082</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -4459,7 +7482,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="4">
         <v>46083</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4480,7 +7503,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="4">
         <v>46084</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4501,7 +7524,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="4">
         <v>46085</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -4522,7 +7545,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="4">
         <v>46086</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -4543,7 +7566,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="4">
         <v>46087</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -4564,7 +7587,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="4">
         <v>46088</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4585,7 +7608,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="4">
         <v>46089</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -4606,7 +7629,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="4">
         <v>46090</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -4627,7 +7650,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="4">
         <v>46091</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -4648,7 +7671,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="4">
         <v>46092</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -4669,7 +7692,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="4">
         <v>46093</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -4690,7 +7713,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="4">
         <v>46094</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -4711,7 +7734,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="4">
         <v>46095</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -4732,7 +7755,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="4">
         <v>46096</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -4753,7 +7776,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="4">
         <v>46097</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -4774,7 +7797,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+      <c r="A18" s="4">
         <v>46098</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -4795,7 +7818,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="A19" s="4">
         <v>46099</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -4816,7 +7839,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+      <c r="A20" s="4">
         <v>46100</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -4837,7 +7860,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="A21" s="4">
         <v>46101</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -4858,7 +7881,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+      <c r="A22" s="4">
         <v>46102</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -4879,7 +7902,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+      <c r="A23" s="4">
         <v>46103</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -4900,7 +7923,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+      <c r="A24" s="4">
         <v>46104</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -4921,7 +7944,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+      <c r="A25" s="4">
         <v>46105</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -4942,7 +7965,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
+      <c r="A26" s="4">
         <v>46106</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -4967,7 +7990,7 @@
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+      <c r="A27" s="4">
         <v>46107</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -4992,7 +8015,7 @@
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+      <c r="A28" s="4">
         <v>46108</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -5013,7 +8036,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+      <c r="A29" s="4">
         <v>46109</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -5034,7 +8057,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
+      <c r="A30" s="4">
         <v>46110</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -5055,7 +8078,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+      <c r="A31" s="4">
         <v>46111</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -5085,122 +8108,392 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A6DD3D-EF38-415D-9341-BAA80CAA7DBA}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>46082</v>
+      </c>
+      <c r="B2" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>46083</v>
+      </c>
+      <c r="B3" s="15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>46084</v>
+      </c>
+      <c r="B4" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B5" s="15">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>46086</v>
+      </c>
+      <c r="B6" s="15">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>46087</v>
+      </c>
+      <c r="B7" s="15">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>46088</v>
+      </c>
+      <c r="B8" s="15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>46089</v>
+      </c>
+      <c r="B9" s="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>46090</v>
+      </c>
+      <c r="B10" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="15">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B12" s="15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B13" s="15">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>46094</v>
+      </c>
+      <c r="B14" s="15">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>46095</v>
+      </c>
+      <c r="B15" s="15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>46096</v>
+      </c>
+      <c r="B16" s="15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>46097</v>
+      </c>
+      <c r="B17" s="15">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>46098</v>
+      </c>
+      <c r="B18" s="15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B19" s="15">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>46100</v>
+      </c>
+      <c r="B20" s="15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>46101</v>
+      </c>
+      <c r="B21" s="15">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>46102</v>
+      </c>
+      <c r="B22" s="15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>46103</v>
+      </c>
+      <c r="B23" s="15">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>46104</v>
+      </c>
+      <c r="B24" s="15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>46105</v>
+      </c>
+      <c r="B25" s="15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B26" s="15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B27" s="15">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>46108</v>
+      </c>
+      <c r="B28" s="15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>46109</v>
+      </c>
+      <c r="B29" s="15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>46110</v>
+      </c>
+      <c r="B30" s="15">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B31" s="15">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="15">
+        <v>13068</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7026F4-D241-41C2-B57E-1B0C082D4501}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="6" t="s">
+    <row r="1" spans="1:17" s="14" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+    <row r="2" spans="1:17" s="14" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
     </row>
-    <row r="3" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
+    <row r="3" spans="1:17" s="14" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
+      <c r="A6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="9">
+        <v>3150</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7">
-        <v>3150</v>
+      <c r="A7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="9">
+        <v>2499</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="7">
-        <v>2499</v>
+      <c r="A8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="9">
+        <v>2450</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="7">
-        <v>2450</v>
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9">
+        <v>2350</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="7">
-        <v>2350</v>
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9">
+        <v>1620</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7">
-        <v>1620</v>
+      <c r="A11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9">
+        <v>999</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B12" s="9">
         <v>13068</v>
       </c>
     </row>
